--- a/results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/anova_taxa.xlsx
+++ b/results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/anova_taxa.xlsx
@@ -490,19 +490,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>368.33</v>
+        <v>331.44</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>32.69</v>
+        <v>13.8</v>
       </c>
       <c r="F2" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="G2" t="n">
-        <v>309.83</v>
+        <v>516.29</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -511,17 +511,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6.10 ± 0.11</t>
+          <t>5.95 ± 0.16</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.45 ± 0.22</t>
+          <t>0.19 ± 0.15</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.22 ± 0.10</t>
+          <t>0.27 ± 0.13</t>
         </is>
       </c>
     </row>
@@ -535,19 +535,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>191.65</v>
+        <v>142.93</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>116.97</v>
+        <v>86.01000000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="G3" t="n">
-        <v>45.06</v>
+        <v>35.73</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -556,17 +556,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.32 ± 0.38</t>
+          <t>1.62 ± 0.42</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>3.03 ± 0.39</t>
+          <t>3.26 ± 0.44</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>5.96 ± 0.07</t>
+          <t>5.95 ± 0.09</t>
         </is>
       </c>
     </row>
@@ -580,38 +580,38 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>110.73</v>
+        <v>64.66</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>137.07</v>
+        <v>128.57</v>
       </c>
       <c r="F4" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="G4" t="n">
-        <v>22.22</v>
+        <v>10.81</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0000***</t>
+          <t>0.0002***</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1.97 ± 0.53</t>
+          <t>2.28 ± 0.54</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.43 ± 0.27</t>
+          <t>5.17 ± 0.37</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>4.00 ± 0.33</t>
+          <t>3.80 ± 0.40</t>
         </is>
       </c>
     </row>
@@ -625,38 +625,38 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>32.25</v>
+        <v>33.98</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>144.99</v>
+        <v>119.78</v>
       </c>
       <c r="F5" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="G5" t="n">
-        <v>6.12</v>
+        <v>6.1</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0040**</t>
+          <t>0.0047**</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.56 ± 0.55</t>
+          <t>2.64 ± 0.56</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.93 ± 0.32</t>
+          <t>0.73 ± 0.36</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.78 ± 0.27</t>
+          <t>0.89 ± 0.33</t>
         </is>
       </c>
     </row>
@@ -670,38 +670,38 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>32.2</v>
+        <v>29.57</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>182.87</v>
+        <v>145.99</v>
       </c>
       <c r="F6" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="G6" t="n">
-        <v>4.84</v>
+        <v>4.35</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0116*</t>
+          <t>0.0190*</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.96 ± 0.36</t>
+          <t>1.18 ± 0.38</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2.82 ± 0.44</t>
+          <t>3.10 ± 0.56</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1.95 ± 0.38</t>
+          <t>1.85 ± 0.43</t>
         </is>
       </c>
     </row>
@@ -711,42 +711,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hexagenia</t>
+          <t>Acari</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3.6</v>
+        <v>3.17</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>43.11</v>
+        <v>25.17</v>
       </c>
       <c r="F7" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="G7" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.1100</t>
+          <t>0.0783.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.22 ± 0.15</t>
+          <t>0.10 ± 0.05</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.13 ± 0.10</t>
+          <t>0.65 ± 0.27</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.69 ± 0.31</t>
+          <t>0.67 ± 0.19</t>
         </is>
       </c>
     </row>
@@ -760,38 +760,38 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6.5</v>
+        <v>9.08</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>78.70999999999999</v>
+        <v>72.72</v>
       </c>
       <c r="F8" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="G8" t="n">
-        <v>2.27</v>
+        <v>2.69</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.1128</t>
+          <t>0.0796.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.03 ± 0.03</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.51 ± 0.26</t>
+          <t>0.71 ± 0.38</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.88 ± 0.35</t>
+          <t>1.11 ± 0.43</t>
         </is>
       </c>
     </row>
@@ -801,42 +801,42 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hydrozoa</t>
+          <t>Hexagenia</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1.44</v>
+        <v>4.84</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>17.53</v>
+        <v>40.28</v>
       </c>
       <c r="F9" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="G9" t="n">
-        <v>2.27</v>
+        <v>2.58</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.1133</t>
+          <t>0.0872.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.49 ± 0.23</t>
+          <t>0.22 ± 0.15</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.17 ± 0.10</t>
+          <t>0.15 ± 0.15</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.09 ± 0.06</t>
+          <t>0.87 ± 0.38</t>
         </is>
       </c>
     </row>
@@ -846,42 +846,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Turbellaria</t>
+          <t>Hydrozoa</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="D10" t="n">
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>19.78</v>
+        <v>13.49</v>
       </c>
       <c r="F10" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="G10" t="n">
-        <v>2.12</v>
+        <v>2.54</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.1296</t>
+          <t>0.0906.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.48 ± 0.28</t>
+          <t>0.49 ± 0.23</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.10 ± 0.06</t>
+          <t>0.07 ± 0.07</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.12 ± 0.07</t>
+          <t>0.11 ± 0.08</t>
         </is>
       </c>
     </row>
@@ -891,42 +891,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Acari</t>
+          <t>Turbellaria</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="D11" t="n">
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>28.55</v>
+        <v>17.46</v>
       </c>
       <c r="F11" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="G11" t="n">
-        <v>1.87</v>
+        <v>2.53</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.1633</t>
+          <t>0.0917.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.07 ± 0.05</t>
+          <t>0.52 ± 0.27</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.45 ± 0.19</t>
+          <t>0.05 ± 0.05</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.53 ± 0.16</t>
+          <t>0.10 ± 0.08</t>
         </is>
       </c>
     </row>
@@ -940,23 +940,23 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1.35</v>
+        <v>2.11</v>
       </c>
       <c r="D12" t="n">
         <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>22.58</v>
+        <v>18.46</v>
       </c>
       <c r="F12" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="G12" t="n">
-        <v>1.64</v>
+        <v>2.46</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.2035</t>
+          <t>0.0974.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.11 ± 0.08</t>
+          <t>0.05 ± 0.05</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.38 ± 0.23</t>
+          <t>0.48 ± 0.29</t>
         </is>
       </c>
     </row>
@@ -981,42 +981,42 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Gastropoda</t>
+          <t>Ceratopogonidae</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.95</v>
+        <v>0.37</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>61.97</v>
+        <v>4.11</v>
       </c>
       <c r="F13" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="G13" t="n">
-        <v>1.31</v>
+        <v>1.95</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.2786</t>
+          <t>0.1550</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.12 ± 0.10</t>
+          <t>0.03 ± 0.03</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.67 ± 0.29</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.38 ± 0.20</t>
+          <t>0.20 ± 0.14</t>
         </is>
       </c>
     </row>
@@ -1026,42 +1026,42 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ceratopogonidae</t>
+          <t>Hydropsychidae</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.22</v>
+        <v>0.72</v>
       </c>
       <c r="D14" t="n">
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>5.59</v>
+        <v>13.06</v>
       </c>
       <c r="F14" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="G14" t="n">
-        <v>1.1</v>
+        <v>1.19</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.3398</t>
+          <t>0.3129</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.42 ± 0.16</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.07 ± 0.05</t>
+          <t>0.12 ± 0.12</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.16 ± 0.11</t>
+          <t>0.26 ± 0.14</t>
         </is>
       </c>
     </row>
@@ -1071,42 +1071,42 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Hydropsychidae</t>
+          <t>Other Trichoptera</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.7</v>
+        <v>0.18</v>
       </c>
       <c r="D15" t="n">
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>17.67</v>
+        <v>3.77</v>
       </c>
       <c r="F15" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="G15" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.3430</t>
+          <t>0.3639</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.36 ± 0.16</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.12 ± 0.09</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.33 ± 0.16</t>
+          <t>0.13 ± 0.13</t>
         </is>
       </c>
     </row>
@@ -1116,42 +1116,42 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Other Trichoptera</t>
+          <t>Gastropoda</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.11</v>
+        <v>2.06</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>6.7</v>
+        <v>48.91</v>
       </c>
       <c r="F16" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="G16" t="n">
-        <v>0.45</v>
+        <v>0.91</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.6385</t>
+          <t>0.4117</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.20 ± 0.12</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.09 ± 0.07</t>
+          <t>0.69 ± 0.39</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.11 ± 0.11</t>
+          <t>0.32 ± 0.21</t>
         </is>
       </c>
     </row>
@@ -1165,23 +1165,23 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="D17" t="n">
         <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>48.69</v>
+        <v>39.85</v>
       </c>
       <c r="F17" t="n">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="G17" t="n">
-        <v>0.44</v>
+        <v>0.43</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.6460</t>
+          <t>0.6560</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1191,12 +1191,12 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.51 ± 0.26</t>
+          <t>0.54 ± 0.35</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.32 ± 0.12</t>
+          <t>0.31 ± 0.13</t>
         </is>
       </c>
     </row>
@@ -1234,10 +1234,10 @@
         <v>15</v>
       </c>
       <c r="J19" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="K19" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">

--- a/results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/anova_taxa.xlsx
+++ b/results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/anova_taxa.xlsx
@@ -490,19 +490,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>331.44</v>
+        <v>343.6</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>13.8</v>
+        <v>28.32</v>
       </c>
       <c r="F2" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G2" t="n">
-        <v>516.29</v>
+        <v>303.28</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -511,17 +511,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5.95 ± 0.16</t>
+          <t>6.07 ± 0.12</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.19 ± 0.15</t>
+          <t>0.35 ± 0.23</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.27 ± 0.13</t>
+          <t>0.23 ± 0.11</t>
         </is>
       </c>
     </row>
@@ -535,19 +535,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>142.93</v>
+        <v>173.27</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>86.01000000000001</v>
+        <v>101.88</v>
       </c>
       <c r="F3" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G3" t="n">
-        <v>35.73</v>
+        <v>42.52</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -556,17 +556,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.62 ± 0.42</t>
+          <t>1.41 ± 0.40</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>3.26 ± 0.44</t>
+          <t>3.04 ± 0.41</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>5.95 ± 0.09</t>
+          <t>5.95 ± 0.08</t>
         </is>
       </c>
     </row>
@@ -580,38 +580,38 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>64.66</v>
+        <v>88.13</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>128.57</v>
+        <v>130.69</v>
       </c>
       <c r="F4" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G4" t="n">
-        <v>10.81</v>
+        <v>16.86</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0002***</t>
+          <t>0.0000***</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.28 ± 0.54</t>
+          <t>2.11 ± 0.55</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.17 ± 0.37</t>
+          <t>5.35 ± 0.30</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>3.80 ± 0.40</t>
+          <t>3.98 ± 0.34</t>
         </is>
       </c>
     </row>
@@ -621,42 +621,42 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Amphipoda</t>
+          <t>Nematoda</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>33.98</v>
+        <v>35.94</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>119.78</v>
+        <v>164.3</v>
       </c>
       <c r="F5" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G5" t="n">
-        <v>6.1</v>
+        <v>5.47</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0047**</t>
+          <t>0.0071**</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.64 ± 0.56</t>
+          <t>1.03 ± 0.38</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.73 ± 0.36</t>
+          <t>3.07 ± 0.46</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.89 ± 0.33</t>
+          <t>1.94 ± 0.40</t>
         </is>
       </c>
     </row>
@@ -666,42 +666,42 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nematoda</t>
+          <t>Amphipoda</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>29.57</v>
+        <v>29.15</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>145.99</v>
+        <v>133.57</v>
       </c>
       <c r="F6" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G6" t="n">
-        <v>4.35</v>
+        <v>5.45</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0190*</t>
+          <t>0.0072**</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1.18 ± 0.38</t>
+          <t>2.51 ± 0.59</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>3.10 ± 0.56</t>
+          <t>0.83 ± 0.33</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>1.85 ± 0.43</t>
+          <t>0.82 ± 0.28</t>
         </is>
       </c>
     </row>
@@ -711,42 +711,42 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Acari</t>
+          <t>Hydrozoa</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3.17</v>
+        <v>1.81</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>25.17</v>
+        <v>14.49</v>
       </c>
       <c r="F7" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G7" t="n">
-        <v>2.7</v>
+        <v>3.12</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.0783.</t>
+          <t>0.0530.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.10 ± 0.05</t>
+          <t>0.52 ± 0.24</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.65 ± 0.27</t>
+          <t>0.11 ± 0.08</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.67 ± 0.19</t>
+          <t>0.09 ± 0.06</t>
         </is>
       </c>
     </row>
@@ -756,42 +756,42 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Caenis</t>
+          <t>Turbellaria</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>9.08</v>
+        <v>2.04</v>
       </c>
       <c r="D8" t="n">
         <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>72.72</v>
+        <v>17.75</v>
       </c>
       <c r="F8" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G8" t="n">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.0796.</t>
+          <t>0.0655.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.03 ± 0.03</t>
+          <t>0.52 ± 0.29</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.71 ± 0.38</t>
+          <t>0.06 ± 0.04</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>1.11 ± 0.43</t>
+          <t>0.08 ± 0.06</t>
         </is>
       </c>
     </row>
@@ -805,38 +805,38 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>4.84</v>
+        <v>3.92</v>
       </c>
       <c r="D9" t="n">
         <v>2</v>
       </c>
       <c r="E9" t="n">
-        <v>40.28</v>
+        <v>42.21</v>
       </c>
       <c r="F9" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G9" t="n">
-        <v>2.58</v>
+        <v>2.32</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.0872.</t>
+          <t>0.1089</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.22 ± 0.15</t>
+          <t>0.23 ± 0.16</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.15 ± 0.15</t>
+          <t>0.11 ± 0.11</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.87 ± 0.38</t>
+          <t>0.72 ± 0.32</t>
         </is>
       </c>
     </row>
@@ -846,42 +846,42 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hydrozoa</t>
+          <t>Hirudinea</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.59</v>
+        <v>1.71</v>
       </c>
       <c r="D10" t="n">
         <v>2</v>
       </c>
       <c r="E10" t="n">
-        <v>13.49</v>
+        <v>19.05</v>
       </c>
       <c r="F10" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G10" t="n">
-        <v>2.54</v>
+        <v>2.24</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.0906.</t>
+          <t>0.1167</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.49 ± 0.23</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.07 ± 0.07</t>
+          <t>0.04 ± 0.04</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.11 ± 0.08</t>
+          <t>0.40 ± 0.25</t>
         </is>
       </c>
     </row>
@@ -891,42 +891,42 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Turbellaria</t>
+          <t>Caenis</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2.05</v>
+        <v>6.81</v>
       </c>
       <c r="D11" t="n">
         <v>2</v>
       </c>
       <c r="E11" t="n">
-        <v>17.46</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G11" t="n">
-        <v>2.53</v>
+        <v>2.2</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.0917.</t>
+          <t>0.1211</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.52 ± 0.27</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.05 ± 0.05</t>
+          <t>0.56 ± 0.29</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.10 ± 0.08</t>
+          <t>0.93 ± 0.37</t>
         </is>
       </c>
     </row>
@@ -936,42 +936,42 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hirudinea</t>
+          <t>Acari</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="D12" t="n">
         <v>2</v>
       </c>
       <c r="E12" t="n">
-        <v>18.46</v>
+        <v>27.56</v>
       </c>
       <c r="F12" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G12" t="n">
-        <v>2.46</v>
+        <v>1.96</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.0974.</t>
+          <t>0.1518</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.08 ± 0.05</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.05 ± 0.05</t>
+          <t>0.51 ± 0.21</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>0.48 ± 0.29</t>
+          <t>0.56 ± 0.17</t>
         </is>
       </c>
     </row>
@@ -981,42 +981,42 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Ceratopogonidae</t>
+          <t>Gastropoda</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.37</v>
+        <v>2.32</v>
       </c>
       <c r="D13" t="n">
         <v>2</v>
       </c>
       <c r="E13" t="n">
-        <v>4.11</v>
+        <v>49.67</v>
       </c>
       <c r="F13" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G13" t="n">
-        <v>1.95</v>
+        <v>1.17</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.1550</t>
+          <t>0.3192</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.03 ± 0.03</t>
+          <t>0.13 ± 0.10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.62 ± 0.30</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>0.20 ± 0.14</t>
+          <t>0.26 ± 0.17</t>
         </is>
       </c>
     </row>
@@ -1026,42 +1026,42 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hydropsychidae</t>
+          <t>Ceratopogonidae</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.72</v>
+        <v>0.23</v>
       </c>
       <c r="D14" t="n">
         <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>13.06</v>
+        <v>5.55</v>
       </c>
       <c r="F14" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G14" t="n">
-        <v>1.19</v>
+        <v>1.04</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.3129</t>
+          <t>0.3606</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.42 ± 0.16</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.12 ± 0.12</t>
+          <t>0.08 ± 0.06</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.26 ± 0.14</t>
+          <t>0.17 ± 0.12</t>
         </is>
       </c>
     </row>
@@ -1075,23 +1075,23 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.18</v>
+        <v>0.15</v>
       </c>
       <c r="D15" t="n">
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3.77</v>
+        <v>3.82</v>
       </c>
       <c r="F15" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G15" t="n">
-        <v>1.03</v>
+        <v>0.97</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.3639</t>
+          <t>0.3857</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.13 ± 0.13</t>
+          <t>0.11 ± 0.11</t>
         </is>
       </c>
     </row>
@@ -1116,42 +1116,42 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Gastropoda</t>
+          <t>Hydropsychidae</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2.06</v>
+        <v>0.66</v>
       </c>
       <c r="D16" t="n">
         <v>2</v>
       </c>
       <c r="E16" t="n">
-        <v>48.91</v>
+        <v>17.37</v>
       </c>
       <c r="F16" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G16" t="n">
-        <v>0.91</v>
+        <v>0.95</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.4117</t>
+          <t>0.3929</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.20 ± 0.12</t>
+          <t>0.38 ± 0.17</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.69 ± 0.39</t>
+          <t>0.13 ± 0.10</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>0.32 ± 0.21</t>
+          <t>0.34 ± 0.16</t>
         </is>
       </c>
     </row>
@@ -1165,38 +1165,38 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.79</v>
+        <v>0.31</v>
       </c>
       <c r="D17" t="n">
         <v>2</v>
       </c>
       <c r="E17" t="n">
-        <v>39.85</v>
+        <v>41.15</v>
       </c>
       <c r="F17" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="G17" t="n">
-        <v>0.43</v>
+        <v>0.19</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.6560</t>
+          <t>0.8291</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.24 ± 0.18</t>
+          <t>0.26 ± 0.19</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.54 ± 0.35</t>
+          <t>0.41 ± 0.27</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.31 ± 0.13</t>
+          <t>0.26 ± 0.11</t>
         </is>
       </c>
     </row>
@@ -1231,13 +1231,13 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J19" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K19" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="20">

--- a/results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/anova_taxa.xlsx
+++ b/results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/anova_taxa.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,11 +474,6 @@
           <t>Cluster C2</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Cluster C3</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
@@ -490,19 +485,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>343.6</v>
+        <v>280.5</v>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>28.32</v>
+        <v>13.12</v>
       </c>
       <c r="F2" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G2" t="n">
-        <v>303.28</v>
+        <v>812.65</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -511,17 +506,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>6.07 ± 0.12</t>
+          <t>5.89 ± 0.18</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.35 ± 0.23</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.23 ± 0.11</t>
+          <t>0.24 ± 0.11</t>
         </is>
       </c>
     </row>
@@ -535,19 +525,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>173.27</v>
+        <v>71.7</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>101.88</v>
+        <v>119.69</v>
       </c>
       <c r="F3" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G3" t="n">
-        <v>42.52</v>
+        <v>22.76</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -556,17 +546,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.41 ± 0.40</t>
+          <t>1.74 ± 0.47</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>3.04 ± 0.41</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>5.95 ± 0.08</t>
+          <t>4.60 ± 0.35</t>
         </is>
       </c>
     </row>
@@ -580,38 +565,33 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>88.13</v>
+        <v>31.88</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>130.69</v>
+        <v>119.9</v>
       </c>
       <c r="F4" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G4" t="n">
-        <v>16.86</v>
+        <v>10.1</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0000***</t>
+          <t>0.0029**</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.11 ± 0.55</t>
+          <t>2.63 ± 0.57</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.35 ± 0.30</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>3.98 ± 0.34</t>
+          <t>4.53 ± 0.32</t>
         </is>
       </c>
     </row>
@@ -621,42 +601,37 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Nematoda</t>
+          <t>Amphipoda</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>35.94</v>
+        <v>22.22</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>164.3</v>
+        <v>109.94</v>
       </c>
       <c r="F5" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G5" t="n">
-        <v>5.47</v>
+        <v>7.68</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0071**</t>
+          <t>0.0086**</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.03 ± 0.38</t>
+          <t>2.42 ± 0.63</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>3.07 ± 0.46</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>1.94 ± 0.40</t>
+          <t>0.83 ± 0.26</t>
         </is>
       </c>
     </row>
@@ -666,42 +641,37 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Amphipoda</t>
+          <t>Turbellaria</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>29.15</v>
+        <v>2.35</v>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>133.57</v>
+        <v>16.84</v>
       </c>
       <c r="F6" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G6" t="n">
-        <v>5.45</v>
+        <v>5.31</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0072**</t>
+          <t>0.0267*</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.51 ± 0.59</t>
+          <t>0.60 ± 0.31</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.83 ± 0.33</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0.82 ± 0.28</t>
+          <t>0.08 ± 0.05</t>
         </is>
       </c>
     </row>
@@ -711,42 +681,37 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hydrozoa</t>
+          <t>Acari</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>14.49</v>
+        <v>15.03</v>
       </c>
       <c r="F7" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G7" t="n">
-        <v>3.12</v>
+        <v>4.7</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.0530.</t>
+          <t>0.0366*</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.52 ± 0.24</t>
+          <t>0.12 ± 0.06</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.11 ± 0.08</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0.09 ± 0.06</t>
+          <t>0.58 ± 0.14</t>
         </is>
       </c>
     </row>
@@ -756,42 +721,37 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Turbellaria</t>
+          <t>Hydrozoa</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.04</v>
+        <v>1.44</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>17.75</v>
+        <v>13.19</v>
       </c>
       <c r="F8" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G8" t="n">
-        <v>2.88</v>
+        <v>4.15</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.0655.</t>
+          <t>0.0487*</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.52 ± 0.29</t>
+          <t>0.51 ± 0.26</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.06 ± 0.04</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0.08 ± 0.06</t>
+          <t>0.10 ± 0.06</t>
         </is>
       </c>
     </row>
@@ -801,42 +761,37 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Hexagenia</t>
+          <t>Caenis</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3.92</v>
+        <v>6.57</v>
       </c>
       <c r="D9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>42.21</v>
+        <v>70.12</v>
       </c>
       <c r="F9" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G9" t="n">
-        <v>2.32</v>
+        <v>3.56</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.1089</t>
+          <t>0.0669.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.23 ± 0.16</t>
+          <t>0.03 ± 0.03</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.11 ± 0.11</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0.72 ± 0.32</t>
+          <t>0.90 ± 0.32</t>
         </is>
       </c>
     </row>
@@ -846,42 +801,37 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hirudinea</t>
+          <t>Nematoda</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1.71</v>
+        <v>12.53</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>19.05</v>
+        <v>148.96</v>
       </c>
       <c r="F10" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G10" t="n">
-        <v>2.24</v>
+        <v>3.2</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.1167</t>
+          <t>0.0818.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>1.31 ± 0.43</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.04 ± 0.04</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0.40 ± 0.25</t>
+          <t>2.51 ± 0.41</t>
         </is>
       </c>
     </row>
@@ -891,42 +841,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Caenis</t>
+          <t>Hydropsychidae</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>6.81</v>
+        <v>0.65</v>
       </c>
       <c r="D11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>77.31999999999999</v>
+        <v>12.65</v>
       </c>
       <c r="F11" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G11" t="n">
-        <v>2.2</v>
+        <v>1.94</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.1211</t>
+          <t>0.1717</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.49 ± 0.18</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.56 ± 0.29</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0.93 ± 0.37</t>
+          <t>0.22 ± 0.10</t>
         </is>
       </c>
     </row>
@@ -936,42 +881,37 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Acari</t>
+          <t>Hexagenia</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.16</v>
+        <v>1.55</v>
       </c>
       <c r="D12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>27.56</v>
+        <v>39.39</v>
       </c>
       <c r="F12" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G12" t="n">
-        <v>1.96</v>
+        <v>1.49</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.1518</t>
+          <t>0.2292</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.08 ± 0.05</t>
+          <t>0.10 ± 0.10</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>0.51 ± 0.21</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0.56 ± 0.17</t>
+          <t>0.52 ± 0.23</t>
         </is>
       </c>
     </row>
@@ -981,42 +921,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Gastropoda</t>
+          <t>Hirudinea</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.32</v>
+        <v>0.68</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>49.67</v>
+        <v>19.63</v>
       </c>
       <c r="F13" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G13" t="n">
-        <v>1.17</v>
+        <v>1.31</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>0.3192</t>
+          <t>0.2595</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.13 ± 0.10</t>
+          <t>0.00 ± 0.00</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.62 ± 0.30</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>0.26 ± 0.17</t>
+          <t>0.28 ± 0.17</t>
         </is>
       </c>
     </row>
@@ -1026,42 +961,37 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ceratopogonidae</t>
+          <t>Gastropoda</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.23</v>
+        <v>1.03</v>
       </c>
       <c r="D14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>5.55</v>
+        <v>49.01</v>
       </c>
       <c r="F14" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G14" t="n">
-        <v>1.04</v>
+        <v>0.8</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.3606</t>
+          <t>0.3762</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
+          <t>0.23 ± 0.14</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.08 ± 0.06</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>0.17 ± 0.12</t>
+          <t>0.57 ± 0.26</t>
         </is>
       </c>
     </row>
@@ -1075,23 +1005,23 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="D15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>3.82</v>
+        <v>3.89</v>
       </c>
       <c r="F15" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G15" t="n">
-        <v>0.97</v>
+        <v>0.48</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.3857</t>
+          <t>0.4949</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1101,12 +1031,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.00 ± 0.00</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0.11 ± 0.11</t>
+          <t>0.07 ± 0.07</t>
         </is>
       </c>
     </row>
@@ -1116,42 +1041,37 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hydropsychidae</t>
+          <t>Ceratopogonidae</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.66</v>
+        <v>0.04</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>17.37</v>
+        <v>4.24</v>
       </c>
       <c r="F16" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G16" t="n">
-        <v>0.95</v>
+        <v>0.32</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>0.3929</t>
+          <t>0.5751</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>0.38 ± 0.17</t>
+          <t>0.03 ± 0.03</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>0.13 ± 0.10</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>0.34 ± 0.16</t>
+          <t>0.09 ± 0.08</t>
         </is>
       </c>
     </row>
@@ -1165,38 +1085,33 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.31</v>
+        <v>0.01</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>41.15</v>
+        <v>12.28</v>
       </c>
       <c r="F17" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="G17" t="n">
-        <v>0.19</v>
+        <v>0.03</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.8291</t>
+          <t>0.8598</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.26 ± 0.19</t>
+          <t>0.28 ± 0.21</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.41 ± 0.27</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>0.26 ± 0.11</t>
+          <t>0.24 ± 0.09</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1128,6 @@
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
@@ -1231,13 +1145,10 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="J19" t="n">
-        <v>21</v>
-      </c>
-      <c r="K19" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -1253,7 +1164,6 @@
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
@@ -1272,7 +1182,6 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
